--- a/flowers.xlsx
+++ b/flowers.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/murielinard/Documents/flower_bot/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C88E4EB9-3A47-4944-895D-6CD4E702A8C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C431359-9290-4244-9A81-5A71521425EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="660" windowWidth="14980" windowHeight="17040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3119" uniqueCount="2254">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3125" uniqueCount="2259">
   <si>
     <t>Chinese</t>
   </si>
@@ -6782,15 +6782,37 @@
   </si>
   <si>
     <t>https://raw.githubusercontent.com/im773312mi/Flowers/refs/heads/main/Bamboo%20in%20Gold.png</t>
+  </si>
+  <si>
+    <t>霽粉山月桂.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/im773312mi/Flowers/refs/heads/main/%E9%9C%BD%E7%B2%89%E5%B1%B1%E6%9C%88%E6%A1%82.png</t>
+  </si>
+  <si>
+    <t>霽粉山月桂</t>
+  </si>
+  <si>
+    <t>網羅幸運的溫暖、獨一無二的真摯心意</t>
+  </si>
+  <si>
+    <t>雨過天晴的柔情、歷經風雨後的希望</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -6853,19 +6875,20 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="top"/>
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -7182,8 +7205,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G520"/>
+  <dimension ref="A1:G521"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="115" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
@@ -17760,6 +17788,26 @@
       </c>
       <c r="E520" t="s">
         <v>2248</v>
+      </c>
+      <c r="G520" t="s">
+        <v>2258</v>
+      </c>
+    </row>
+    <row r="521" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+      <c r="A521" t="s">
+        <v>2256</v>
+      </c>
+      <c r="C521" s="5" t="s">
+        <v>875</v>
+      </c>
+      <c r="D521" t="s">
+        <v>2254</v>
+      </c>
+      <c r="E521" t="s">
+        <v>2255</v>
+      </c>
+      <c r="G521" t="s">
+        <v>2257</v>
       </c>
     </row>
   </sheetData>

--- a/flowers.xlsx
+++ b/flowers.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/murielinard/Documents/flower_bot/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C431359-9290-4244-9A81-5A71521425EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F53576F4-99F4-FC4A-8F79-7AE602499B57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="660" windowWidth="14980" windowHeight="17040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3125" uniqueCount="2259">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3165" uniqueCount="2291">
   <si>
     <t>Chinese</t>
   </si>
@@ -6797,6 +6797,102 @@
   </si>
   <si>
     <t>雨過天晴的柔情、歷經風雨後的希望</t>
+  </si>
+  <si>
+    <t>杏壇啟學</t>
+  </si>
+  <si>
+    <t>桃李承輝</t>
+  </si>
+  <si>
+    <t>紫褐墨蘭</t>
+  </si>
+  <si>
+    <t>杏壇啟學.png</t>
+  </si>
+  <si>
+    <t>桃李承輝.png</t>
+  </si>
+  <si>
+    <t>紫褐墨蘭.png</t>
+  </si>
+  <si>
+    <t>默默奉獻的高潔、深沉內斂的師恩</t>
+  </si>
+  <si>
+    <t>智慧的啟蒙、傳道授業的崇高恩情</t>
+  </si>
+  <si>
+    <t>桃李滿門的碩果、薪火相傳的無限榮光</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/im773312mi/Flowers/refs/heads/main/%E7%B4%AB%E8%A4%90%E5%A2%A8%E8%98%AD.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/im773312mi/Flowers/refs/heads/main/%E6%9D%8F%E5%A3%87%E5%95%9F%E5%AD%B8.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/im773312mi/Flowers/refs/heads/main/%E6%A1%83%E6%9D%8E%E6%89%BF%E8%BC%9D.png</t>
+  </si>
+  <si>
+    <t>赤丹鳳凰花</t>
+  </si>
+  <si>
+    <t>宮粉玉葉金花</t>
+  </si>
+  <si>
+    <t>雲峰龍吐珠</t>
+  </si>
+  <si>
+    <t>絳紅玉葉金花</t>
+  </si>
+  <si>
+    <t>雲白玉葉金花</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/im773312mi/Flowers/refs/heads/main/%E8%B5%A4%E4%B8%B9%E9%B3%B3%E5%87%B0%E8%8A%B1.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/im773312mi/Flowers/refs/heads/main/%E9%9B%B2%E5%B3%B0%E9%BE%8D%E5%90%90%E7%8F%A0.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/im773312mi/Flowers/refs/heads/main/%E9%9B%B2%E7%99%BD%E7%8E%89%E8%91%89%E9%87%91%E8%8A%B1.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/im773312mi/Flowers/refs/heads/main/%E7%B5%B3%E7%B4%85%E7%8E%89%E8%91%89%E9%87%91%E8%8A%B1.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/im773312mi/Flowers/refs/heads/main/%E5%AE%AE%E7%B2%89%E7%8E%89%E8%91%89%E9%87%91%E8%8A%B1.png</t>
+  </si>
+  <si>
+    <t>赤丹鳳凰花.png</t>
+  </si>
+  <si>
+    <t>宮粉玉葉金花.png</t>
+  </si>
+  <si>
+    <t>雲峰龍吐珠.png</t>
+  </si>
+  <si>
+    <t>絳紅玉葉金花.png</t>
+  </si>
+  <si>
+    <t>雲白玉葉金花.png</t>
+  </si>
+  <si>
+    <t>熾熱的思念、熱情奔放的青春</t>
+  </si>
+  <si>
+    <t>柔美高貴、溫柔的守護</t>
+  </si>
+  <si>
+    <t>珍貴的希望、吉祥如意</t>
+  </si>
+  <si>
+    <t>濃烈的心意、熱情堅定</t>
+  </si>
+  <si>
+    <t>純潔無暇的守候、點亮迷途的星光</t>
   </si>
 </sst>
 </file>
@@ -7205,12 +7301,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G521"/>
+  <dimension ref="A1:G529"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.1640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="13.6640625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="115" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="120.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.2">
@@ -17808,6 +17905,157 @@
       </c>
       <c r="G521" t="s">
         <v>2257</v>
+      </c>
+    </row>
+    <row r="522" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A522" t="s">
+        <v>2259</v>
+      </c>
+      <c r="C522" t="s">
+        <v>874</v>
+      </c>
+      <c r="D522" t="s">
+        <v>2262</v>
+      </c>
+      <c r="E522" t="s">
+        <v>2269</v>
+      </c>
+      <c r="G522" t="s">
+        <v>2266</v>
+      </c>
+    </row>
+    <row r="523" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A523" t="s">
+        <v>2260</v>
+      </c>
+      <c r="C523" t="s">
+        <v>874</v>
+      </c>
+      <c r="D523" t="s">
+        <v>2263</v>
+      </c>
+      <c r="E523" t="s">
+        <v>2270</v>
+      </c>
+      <c r="G523" t="s">
+        <v>2267</v>
+      </c>
+    </row>
+    <row r="524" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A524" t="s">
+        <v>2261</v>
+      </c>
+      <c r="C524" t="s">
+        <v>877</v>
+      </c>
+      <c r="D524" t="s">
+        <v>2264</v>
+      </c>
+      <c r="E524" t="s">
+        <v>2268</v>
+      </c>
+      <c r="G524" t="s">
+        <v>2265</v>
+      </c>
+    </row>
+    <row r="525" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A525" t="s">
+        <v>2271</v>
+      </c>
+      <c r="C525" t="s">
+        <v>876</v>
+      </c>
+      <c r="D525" t="s">
+        <v>2281</v>
+      </c>
+      <c r="E525" t="s">
+        <v>2276</v>
+      </c>
+      <c r="F525">
+        <v>65</v>
+      </c>
+      <c r="G525" t="s">
+        <v>2286</v>
+      </c>
+    </row>
+    <row r="526" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A526" t="s">
+        <v>2272</v>
+      </c>
+      <c r="C526" t="s">
+        <v>876</v>
+      </c>
+      <c r="D526" t="s">
+        <v>2282</v>
+      </c>
+      <c r="E526" t="s">
+        <v>2280</v>
+      </c>
+      <c r="F526">
+        <v>64</v>
+      </c>
+      <c r="G526" t="s">
+        <v>2287</v>
+      </c>
+    </row>
+    <row r="527" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A527" t="s">
+        <v>2273</v>
+      </c>
+      <c r="C527" t="s">
+        <v>876</v>
+      </c>
+      <c r="D527" t="s">
+        <v>2283</v>
+      </c>
+      <c r="E527" t="s">
+        <v>2277</v>
+      </c>
+      <c r="F527">
+        <v>63</v>
+      </c>
+      <c r="G527" t="s">
+        <v>2288</v>
+      </c>
+    </row>
+    <row r="528" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A528" t="s">
+        <v>2274</v>
+      </c>
+      <c r="C528" t="s">
+        <v>876</v>
+      </c>
+      <c r="D528" t="s">
+        <v>2284</v>
+      </c>
+      <c r="E528" t="s">
+        <v>2279</v>
+      </c>
+      <c r="F528">
+        <v>62</v>
+      </c>
+      <c r="G528" t="s">
+        <v>2289</v>
+      </c>
+    </row>
+    <row r="529" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A529" t="s">
+        <v>2275</v>
+      </c>
+      <c r="C529" t="s">
+        <v>876</v>
+      </c>
+      <c r="D529" t="s">
+        <v>2285</v>
+      </c>
+      <c r="E529" t="s">
+        <v>2278</v>
+      </c>
+      <c r="F529">
+        <v>61</v>
+      </c>
+      <c r="G529" t="s">
+        <v>2290</v>
       </c>
     </row>
   </sheetData>
